--- a/data/trans_orig/P33B_R3-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R3-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>139748</t>
+          <t>149313</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124183</t>
+          <t>130568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158247</t>
+          <t>168839</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>284430</t>
+          <t>312206</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>263278</t>
+          <t>287414</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>304280</t>
+          <t>332905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>424178</t>
+          <t>461519</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>395855</t>
+          <t>435019</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>452662</t>
+          <t>490990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>375190</t>
+          <t>429216</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356691</t>
+          <t>409690</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390755</t>
+          <t>447961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>468738</t>
+          <t>509109</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>448888</t>
+          <t>488410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>489890</t>
+          <t>533901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>843929</t>
+          <t>938326</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>815445</t>
+          <t>908855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>872252</t>
+          <t>964826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>278471</t>
+          <t>302543</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>194553</t>
+          <t>273776</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>329449</t>
+          <t>339790</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>353280</t>
+          <t>398440</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>263921</t>
+          <t>368357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>402004</t>
+          <t>430790</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>631751</t>
+          <t>700983</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>508112</t>
+          <t>650900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>710240</t>
+          <t>753665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2010826</t>
+          <t>1926942</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1959848</t>
+          <t>1889695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2094744</t>
+          <t>1955709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1884543</t>
+          <t>1772952</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1835819</t>
+          <t>1740602</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1973902</t>
+          <t>1803035</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3895370</t>
+          <t>3699894</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3816881</t>
+          <t>3647212</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4019009</t>
+          <t>3749977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81951</t>
+          <t>92719</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64026</t>
+          <t>75026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100623</t>
+          <t>117739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>94845</t>
+          <t>109019</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81352</t>
+          <t>93116</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112188</t>
+          <t>127173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>176795</t>
+          <t>201738</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152805</t>
+          <t>177070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202117</t>
+          <t>228922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>563703</t>
+          <t>617880</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>545031</t>
+          <t>592860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>581628</t>
+          <t>635573</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>565618</t>
+          <t>625858</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>548275</t>
+          <t>607704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>579111</t>
+          <t>641761</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1129322</t>
+          <t>1243739</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1104000</t>
+          <t>1216555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1153312</t>
+          <t>1268407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>500169</t>
+          <t>544575</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>384806</t>
+          <t>499372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>558352</t>
+          <t>593304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>732555</t>
+          <t>819665</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>588625</t>
+          <t>775430</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>802156</t>
+          <t>863889</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1232724</t>
+          <t>1364240</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1069728</t>
+          <t>1302047</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1333143</t>
+          <t>1421800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2949721</t>
+          <t>2974038</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2891538</t>
+          <t>2925309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3065084</t>
+          <t>3019241</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2918900</t>
+          <t>2907920</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2849299</t>
+          <t>2863696</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3062830</t>
+          <t>2952155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5868621</t>
+          <t>5881958</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5768202</t>
+          <t>5824398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6031617</t>
+          <t>5944151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3449890</t>
+          <t>3518613</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3449890</t>
+          <t>3518613</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3449890</t>
+          <t>3518613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7101345</t>
+          <t>7246198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7101345</t>
+          <t>7246198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7101345</t>
+          <t>7246198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
